--- a/data/trans_orig/P1428-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2007</t>
+          <t>Población con diagnóstico de artritis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58170</t>
+          <t>57021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109725</t>
+          <t>112315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151197</t>
+          <t>152596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151429</t>
+          <t>152471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199345</t>
+          <t>200296</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>635842</t>
+          <t>636991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>662759</t>
+          <t>662890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>537154</t>
+          <t>535755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>578626</t>
+          <t>576036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1183018</t>
+          <t>1182067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1230934</t>
+          <t>1229892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58803</t>
+          <t>59458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92256</t>
+          <t>92169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144089</t>
+          <t>143611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191717</t>
+          <t>191709</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212442</t>
+          <t>209543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273303</t>
+          <t>271289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>869544</t>
+          <t>869631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>902997</t>
+          <t>902342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>776676</t>
+          <t>776684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>824304</t>
+          <t>824782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1656890</t>
+          <t>1658904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1717751</t>
+          <t>1720650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36316</t>
+          <t>35292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61789</t>
+          <t>62657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102791</t>
+          <t>103654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142738</t>
+          <t>144034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149003</t>
+          <t>147491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195073</t>
+          <t>195909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616720</t>
+          <t>615852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642193</t>
+          <t>643217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>541103</t>
+          <t>539807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581050</t>
+          <t>580187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1167277</t>
+          <t>1166441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1213347</t>
+          <t>1214859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>58415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90120</t>
+          <t>89937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152933</t>
+          <t>151620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200666</t>
+          <t>201414</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>219286</t>
+          <t>223704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280844</t>
+          <t>279724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852102</t>
+          <t>852285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883620</t>
+          <t>883807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>837946</t>
+          <t>837198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>885679</t>
+          <t>886992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1699990</t>
+          <t>1701110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1761548</t>
+          <t>1757130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>208322</t>
+          <t>208868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266808</t>
+          <t>267097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>554495</t>
+          <t>552263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>643555</t>
+          <t>640890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>775323</t>
+          <t>777516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>886437</t>
+          <t>889127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3009735</t>
+          <t>3009446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3068221</t>
+          <t>3067675</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2735642</t>
+          <t>2738307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2824702</t>
+          <t>2826934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5769304</t>
+          <t>5766614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5880418</t>
+          <t>5878225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2012</t>
+          <t>Población con diagnóstico de artritis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29920</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57563</t>
+          <t>56026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78539</t>
+          <t>74768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116896</t>
+          <t>114445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113142</t>
+          <t>114394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160229</t>
+          <t>162884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>645906</t>
+          <t>647443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673549</t>
+          <t>673155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>580154</t>
+          <t>582605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618511</t>
+          <t>622282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1240290</t>
+          <t>1237635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1287377</t>
+          <t>1286125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50436</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>83462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107352</t>
+          <t>104570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150337</t>
+          <t>148980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166870</t>
+          <t>164035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>221361</t>
+          <t>219284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>934783</t>
+          <t>934485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>967511</t>
+          <t>967249</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>878636</t>
+          <t>879993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921621</t>
+          <t>924403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1825560</t>
+          <t>1827637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1880051</t>
+          <t>1882886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40453</t>
+          <t>38961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67792</t>
+          <t>66299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106743</t>
+          <t>103418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90816</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135340</t>
+          <t>135283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717170</t>
+          <t>718662</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739927</t>
+          <t>740569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>670431</t>
+          <t>673756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>709382</t>
+          <t>710875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1399457</t>
+          <t>1399514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1443981</t>
+          <t>1444469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30163</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58678</t>
+          <t>58967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112369</t>
+          <t>111758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157968</t>
+          <t>157815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154682</t>
+          <t>152655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206542</t>
+          <t>204842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>889061</t>
+          <t>888772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917576</t>
+          <t>914791</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>893933</t>
+          <t>894086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>939532</t>
+          <t>940143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1793098</t>
+          <t>1794798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1844958</t>
+          <t>1846985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>150414</t>
+          <t>151392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>206132</t>
+          <t>205192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>401480</t>
+          <t>398302</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>486526</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>566335</t>
+          <t>569815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>662678</t>
+          <t>668340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3220647</t>
+          <t>3221587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3276365</t>
+          <t>3275387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3068572</t>
+          <t>3074753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3153618</t>
+          <t>3156796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6319199</t>
+          <t>6313537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6415542</t>
+          <t>6412062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2016</t>
+          <t>Población con diagnóstico de artritis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40564</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65156</t>
+          <t>64440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99287</t>
+          <t>98652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92543</t>
+          <t>92651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133753</t>
+          <t>131727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>634236</t>
+          <t>630487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>655524</t>
+          <t>654539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>573552</t>
+          <t>574187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>607683</t>
+          <t>608399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1213886</t>
+          <t>1215912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1255096</t>
+          <t>1254988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48057</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92807</t>
+          <t>91880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135140</t>
+          <t>133239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123157</t>
+          <t>122746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171950</t>
+          <t>170442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974374</t>
+          <t>974681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997858</t>
+          <t>997763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>907773</t>
+          <t>909674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>950106</t>
+          <t>951033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1893394</t>
+          <t>1894902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1942187</t>
+          <t>1942598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19882</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41620</t>
+          <t>42715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>42316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75755</t>
+          <t>75711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72409</t>
+          <t>70812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110035</t>
+          <t>109028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717932</t>
+          <t>716837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739670</t>
+          <t>738888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>709256</t>
+          <t>709300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>740355</t>
+          <t>742695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1434528</t>
+          <t>1435535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1472154</t>
+          <t>1473751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>40758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62283</t>
+          <t>62312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>89097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131796</t>
+          <t>132888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897643</t>
+          <t>896809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918719</t>
+          <t>918477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>943238</t>
+          <t>941618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>981496</t>
+          <t>981467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1849550</t>
+          <t>1848458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1891346</t>
+          <t>1892249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99788</t>
+          <t>101492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142343</t>
+          <t>146115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>294992</t>
+          <t>296250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>369623</t>
+          <t>370515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>411559</t>
+          <t>408237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>500100</t>
+          <t>496976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3252007</t>
+          <t>3248235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3294562</t>
+          <t>3292858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3174919</t>
+          <t>3174027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3249550</t>
+          <t>3248292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6438792</t>
+          <t>6441916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6527333</t>
+          <t>6530655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2023</t>
+          <t>Población con diagnóstico de artritis en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>47977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113497</t>
+          <t>114318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145604</t>
+          <t>145004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186351</t>
+          <t>183632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>585260</t>
+          <t>586591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>606736</t>
+          <t>607670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>529378</t>
+          <t>530630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560646</t>
+          <t>559825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1122360</t>
+          <t>1125079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1163107</t>
+          <t>1163707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113151</t>
+          <t>112814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144686</t>
+          <t>143817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116211</t>
+          <t>109090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200898</t>
+          <t>202702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1130856</t>
+          <t>1131653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166543</t>
+          <t>1170711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>807919</t>
+          <t>808788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>839454</t>
+          <t>839791</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1942417</t>
+          <t>1940613</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2027104</t>
+          <t>2034225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49298</t>
+          <t>49246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89399</t>
+          <t>90607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>601868</t>
+          <t>596230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120454</t>
+          <t>122027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>776457</t>
+          <t>767576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,08%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653667</t>
+          <t>653719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>676112</t>
+          <t>675657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325514</t>
+          <t>331152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>837983</t>
+          <t>836775</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853890</t>
+          <t>862771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1509893</t>
+          <t>1508320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45019</t>
+          <t>46193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71735</t>
+          <t>72420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127227</t>
+          <t>130073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>184488</t>
+          <t>186880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189835</t>
+          <t>188643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245157</t>
+          <t>246663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851956</t>
+          <t>851271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878672</t>
+          <t>877498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906993</t>
+          <t>904601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964254</t>
+          <t>961408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1770015</t>
+          <t>1768509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825337</t>
+          <t>1826529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>136351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>199119</t>
+          <t>202713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>510725</t>
+          <t>508592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1273082</t>
+          <t>1323440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>663265</t>
+          <t>661515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1509503</t>
+          <t>1704021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3252815</t>
+          <t>3249221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3313828</t>
+          <t>3315583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2372529</t>
+          <t>2322171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3134886</t>
+          <t>3137019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5588043</t>
+          <t>5393525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6434281</t>
+          <t>6436031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1428-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>31683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>55940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112315</t>
+          <t>111603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152596</t>
+          <t>152234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152471</t>
+          <t>152031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>200296</t>
+          <t>198980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636991</t>
+          <t>638072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>662890</t>
+          <t>662329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>535755</t>
+          <t>536117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>576036</t>
+          <t>576748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1182067</t>
+          <t>1183383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1229892</t>
+          <t>1230332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59458</t>
+          <t>57011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92169</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143611</t>
+          <t>139490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191709</t>
+          <t>190475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>209543</t>
+          <t>212408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271289</t>
+          <t>271449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>869631</t>
+          <t>871966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>902342</t>
+          <t>904789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>776684</t>
+          <t>777918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>824782</t>
+          <t>828903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1658904</t>
+          <t>1658744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1720650</t>
+          <t>1717785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35292</t>
+          <t>35771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62657</t>
+          <t>62244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103654</t>
+          <t>102440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144034</t>
+          <t>143666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147491</t>
+          <t>149455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195909</t>
+          <t>194743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615852</t>
+          <t>616265</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643217</t>
+          <t>642738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539807</t>
+          <t>540175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>580187</t>
+          <t>581401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1166441</t>
+          <t>1167607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1214859</t>
+          <t>1212895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58415</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89937</t>
+          <t>88682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151620</t>
+          <t>154557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201414</t>
+          <t>200755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223704</t>
+          <t>222563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279724</t>
+          <t>281671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852285</t>
+          <t>853540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883807</t>
+          <t>884841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>837198</t>
+          <t>837857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>886992</t>
+          <t>884055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1701110</t>
+          <t>1699163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1757130</t>
+          <t>1758271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>208868</t>
+          <t>211644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>267097</t>
+          <t>267642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>552263</t>
+          <t>553969</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>640890</t>
+          <t>642144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>777516</t>
+          <t>778081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>889127</t>
+          <t>889635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3009446</t>
+          <t>3008901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3067675</t>
+          <t>3064899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2738307</t>
+          <t>2737053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2826934</t>
+          <t>2825228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5766614</t>
+          <t>5766106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5878225</t>
+          <t>5877660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56026</t>
+          <t>57068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74768</t>
+          <t>76283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114445</t>
+          <t>115169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114394</t>
+          <t>116969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>162884</t>
+          <t>163495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>647443</t>
+          <t>646401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673155</t>
+          <t>673945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582605</t>
+          <t>581881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>622282</t>
+          <t>620767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1237635</t>
+          <t>1237024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1286125</t>
+          <t>1283550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50698</t>
+          <t>50802</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83462</t>
+          <t>82424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104570</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148980</t>
+          <t>148836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164035</t>
+          <t>164798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>219284</t>
+          <t>219050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>934485</t>
+          <t>935523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>967249</t>
+          <t>967145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>879993</t>
+          <t>880137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>924403</t>
+          <t>923515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1827637</t>
+          <t>1827871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1882886</t>
+          <t>1882123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66299</t>
+          <t>67063</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103418</t>
+          <t>103066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>91033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135283</t>
+          <t>133605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>718662</t>
+          <t>717630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>740569</t>
+          <t>739754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673756</t>
+          <t>674108</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>710875</t>
+          <t>710111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1399514</t>
+          <t>1401192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1444469</t>
+          <t>1443764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58967</t>
+          <t>60002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111758</t>
+          <t>113888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157815</t>
+          <t>157731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152655</t>
+          <t>150945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204842</t>
+          <t>204398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888772</t>
+          <t>887737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914791</t>
+          <t>915676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>894086</t>
+          <t>894170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>940143</t>
+          <t>938013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1794798</t>
+          <t>1795242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1846985</t>
+          <t>1848695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151392</t>
+          <t>150975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205192</t>
+          <t>206819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>398302</t>
+          <t>401719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>480345</t>
+          <t>481574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>569815</t>
+          <t>572809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>668340</t>
+          <t>671632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3221587</t>
+          <t>3219960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3275387</t>
+          <t>3275804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3074753</t>
+          <t>3073524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3156796</t>
+          <t>3153379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6313537</t>
+          <t>6310245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6412062</t>
+          <t>6409068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44313</t>
+          <t>41311</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64440</t>
+          <t>65889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98652</t>
+          <t>102180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>92013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131727</t>
+          <t>131629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>630487</t>
+          <t>633489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>654539</t>
+          <t>654580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>574187</t>
+          <t>570659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>608399</t>
+          <t>606950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1215912</t>
+          <t>1216010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1254988</t>
+          <t>1255626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>48165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91880</t>
+          <t>91913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133239</t>
+          <t>133879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122746</t>
+          <t>122589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>170442</t>
+          <t>171595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974681</t>
+          <t>974266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997763</t>
+          <t>998220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909674</t>
+          <t>909034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>951033</t>
+          <t>951000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1894902</t>
+          <t>1893749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1942598</t>
+          <t>1942755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42715</t>
+          <t>40797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42316</t>
+          <t>45486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75711</t>
+          <t>76169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70812</t>
+          <t>70847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109028</t>
+          <t>109352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>716837</t>
+          <t>718755</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>738888</t>
+          <t>739115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>709300</t>
+          <t>708842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742695</t>
+          <t>739525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1435535</t>
+          <t>1435211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1473751</t>
+          <t>1473716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>42093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62312</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102161</t>
+          <t>100447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89097</t>
+          <t>87733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132888</t>
+          <t>133004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896809</t>
+          <t>895474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918477</t>
+          <t>917606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941618</t>
+          <t>943332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>981467</t>
+          <t>978648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848458</t>
+          <t>1848342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1892249</t>
+          <t>1893613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146115</t>
+          <t>145592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296250</t>
+          <t>298270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>370515</t>
+          <t>371859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>408237</t>
+          <t>412329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>496976</t>
+          <t>494081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3248235</t>
+          <t>3248758</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3292858</t>
+          <t>3293747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3174027</t>
+          <t>3172683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3248292</t>
+          <t>3246272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6441916</t>
+          <t>6444811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6530655</t>
+          <t>6526563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26898</t>
+          <t>27963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47977</t>
+          <t>51068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>127700</t>
+          <t>134225</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114318</t>
+          <t>119023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143513</t>
+          <t>152449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>163744</t>
+          <t>172023</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145004</t>
+          <t>151735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>183632</t>
+          <t>193680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>598524</t>
+          <t>651856</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>586591</t>
+          <t>638586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607670</t>
+          <t>661691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>546443</t>
+          <t>597293</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>530630</t>
+          <t>579069</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>559825</t>
+          <t>612495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1144967</t>
+          <t>1249149</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1125079</t>
+          <t>1227492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1163707</t>
+          <t>1269437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634568</t>
+          <t>689654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634568</t>
+          <t>689654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634568</t>
+          <t>689654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674143</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674143</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674143</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1308711</t>
+          <t>1421172</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1308711</t>
+          <t>1421172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1308711</t>
+          <t>1421172</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>47270</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,27 +6947,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>127957</t>
+          <t>142319</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112814</t>
+          <t>126086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143817</t>
+          <t>160635</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>170856</t>
+          <t>189589</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109090</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202702</t>
+          <t>210666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1147813</t>
+          <t>999332</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1131653</t>
+          <t>985118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1170711</t>
+          <t>1010659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,22 +7060,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>824648</t>
+          <t>921741</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>808788</t>
+          <t>903425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>839791</t>
+          <t>937974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1972459</t>
+          <t>1921073</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1940613</t>
+          <t>1899996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2034225</t>
+          <t>1942880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1190711</t>
+          <t>1046602</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1190711</t>
+          <t>1046602</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1190711</t>
+          <t>1046602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>952605</t>
+          <t>1064060</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>952605</t>
+          <t>1064060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>952605</t>
+          <t>1064060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2143315</t>
+          <t>2110662</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2143315</t>
+          <t>2110662</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2143315</t>
+          <t>2110662</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>40433</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27308</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49246</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>280044</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90607</t>
+          <t>73752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>596230</t>
+          <t>104917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>317142</t>
+          <t>127854</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122027</t>
+          <t>110751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>767576</t>
+          <t>147909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>665867</t>
+          <t>760784</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653719</t>
+          <t>747452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675657</t>
+          <t>771652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>647338</t>
+          <t>718132</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331152</t>
+          <t>700636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>836775</t>
+          <t>731801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1313205</t>
+          <t>1478916</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>862771</t>
+          <t>1458861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1508320</t>
+          <t>1496019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>927382</t>
+          <t>805553</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>927382</t>
+          <t>805553</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>927382</t>
+          <t>805553</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1630347</t>
+          <t>1606770</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1630347</t>
+          <t>1606770</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1630347</t>
+          <t>1606770</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>59606</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>47325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72420</t>
+          <t>73458</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>161489</t>
+          <t>170803</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130073</t>
+          <t>153296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186880</t>
+          <t>193543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>219013</t>
+          <t>230408</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>188643</t>
+          <t>208345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>246663</t>
+          <t>255174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866167</t>
+          <t>927311</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851271</t>
+          <t>913459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877498</t>
+          <t>939592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>929992</t>
+          <t>946376</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>904601</t>
+          <t>923636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961408</t>
+          <t>963883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1796159</t>
+          <t>1873688</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1768509</t>
+          <t>1848922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1826529</t>
+          <t>1895751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>923691</t>
+          <t>986917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>923691</t>
+          <t>986917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>923691</t>
+          <t>986917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091481</t>
+          <t>1117179</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091481</t>
+          <t>1117179</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091481</t>
+          <t>1117179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2015172</t>
+          <t>2104096</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2015172</t>
+          <t>2104096</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2015172</t>
+          <t>2104096</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>160410</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202713</t>
+          <t>210735</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>697191</t>
+          <t>534768</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>508592</t>
+          <t>500818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1323440</t>
+          <t>566276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>870755</t>
+          <t>719874</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>661515</t>
+          <t>673935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1704021</t>
+          <t>757593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3278370</t>
+          <t>3339283</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3249221</t>
+          <t>3313655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3315583</t>
+          <t>3363980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2948420</t>
+          <t>3183542</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2322171</t>
+          <t>3152034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3137019</t>
+          <t>3217492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6226791</t>
+          <t>6522826</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5393525</t>
+          <t>6485107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6436031</t>
+          <t>6568765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
